--- a/public/【纸笔】题型&中文规则一览.xlsx
+++ b/public/【纸笔】题型&中文规则一览.xlsx
@@ -716,7 +716,7 @@
     <t>Tapa</t>
   </si>
   <si>
-    <t>土派艺术</t>
+    <t>土派回路</t>
   </si>
   <si>
     <t>涂黑一些空格，使得所有涂黑的格子连通成一个整体，且没有全部涂黑的2×2结构。格内一个或多个数字表示和此格接触的（至多）八格中所有连续涂黑格段的长度，但不限定顺序。作为特例，一个单独的“0”表示没有和此格接触的涂黑格，而一个单独的问号（格内没有其他问号或数字）也可以代表“0”。</t>
